--- a/03_carrire/履歴書関係/toshiyuki-hioki_履歴書.xlsx
+++ b/03_carrire/履歴書関係/toshiyuki-hioki_履歴書.xlsx
@@ -3741,7 +3741,7 @@
       </c>
       <c r="V10" s="233" t="inlineStr">
         <is>
-          <t>森信建設株式会社　正社員　開始（8月に業務委託へ移行）</t>
+          <t>森信建設株式会社　正社員　開始</t>
         </is>
       </c>
       <c r="W10" s="234" t="n"/>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="V11" s="272" t="inlineStr">
         <is>
-          <t>個人事業主として開業（複数社AI・DX推進アドバイザー）</t>
+          <t>森信建設株式会社　業務委託　再開</t>
         </is>
       </c>
       <c r="W11" s="273" t="n"/>

--- a/03_carrire/履歴書関係/toshiyuki-hioki_履歴書.xlsx
+++ b/03_carrire/履歴書関係/toshiyuki-hioki_履歴書.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="218">
   <si>
     <t>西暦</t>
   </si>
@@ -825,10 +825,7 @@
     <t>2026年8月20日現在</t>
   </si>
   <si>
-    <t>森信建設株式会社　正社員　開始（8月に業務委託へ移行）</t>
-  </si>
-  <si>
-    <t>個人事業主として開業（複数社AI・DX推進アドバイザー）</t>
+    <t>森信建設株式会社　業務委託　再開</t>
   </si>
 </sst>
 </file>
@@ -3894,7 +3891,7 @@
         <v>4</v>
       </c>
       <c r="V10" s="113" t="s">
-        <v>217</v>
+        <v>67</v>
       </c>
       <c r="W10" s="105"/>
       <c r="X10" s="105"/>
@@ -3944,7 +3941,7 @@
         <v>8</v>
       </c>
       <c r="V11" s="114" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="W11" s="115"/>
       <c r="X11" s="115"/>
